--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91323</v>
+        <v>91325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128388490</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128388428</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128388385</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128388354</v>
       </c>
       <c r="B6" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128388540</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -990,41 +990,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>57789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R5" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1075,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,46 +1104,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B6" t="n">
-        <v>57789</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R6" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1184,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -990,46 +990,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B5" t="n">
-        <v>57789</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R5" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,17 +1070,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,41 +1095,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>57789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R6" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,13 +1180,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128388490</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128388428</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128388385</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128388354</v>
       </c>
       <c r="B6" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128388540</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128388490</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128388428</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,41 +990,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>57793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R5" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1075,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,46 +1104,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R6" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1184,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -990,46 +990,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R5" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,17 +1070,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,41 +1095,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>57793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R6" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,13 +1180,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128388490</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128388428</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>128388385</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128388354</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128388540</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128388490</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128388428</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,41 +990,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>57820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R5" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1075,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,46 +1104,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B6" t="n">
-        <v>57820</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R6" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1184,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -990,46 +990,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B5" t="n">
-        <v>57820</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R5" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,17 +1070,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,41 +1095,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>57820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R6" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,13 +1180,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -990,41 +990,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>57820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R5" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1075,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,46 +1104,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B6" t="n">
-        <v>57820</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R6" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1184,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128388490</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128388428</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,46 +990,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B5" t="n">
-        <v>57820</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R5" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,17 +1070,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,41 +1095,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>57824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R6" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,13 +1180,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>128388540</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128388490</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128388428</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128388375</v>
       </c>
       <c r="B4" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,41 +990,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388385</v>
+        <v>128388354</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>57827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774561</v>
+        <v>774556</v>
       </c>
       <c r="R5" t="n">
-        <v>7156599</v>
+        <v>7156558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1075,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,46 +1104,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388354</v>
+        <v>128388385</v>
       </c>
       <c r="B6" t="n">
-        <v>57824</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774556</v>
+        <v>774561</v>
       </c>
       <c r="R6" t="n">
-        <v>7156558</v>
+        <v>7156599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1184,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>128388540</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128388490</v>
+        <v>128388575</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774374</v>
+        <v>774246</v>
       </c>
       <c r="R2" t="n">
-        <v>7156512</v>
+        <v>7156504</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128388428</v>
+        <v>128388710</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,27 +791,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774560</v>
+        <v>774246</v>
       </c>
       <c r="R3" t="n">
-        <v>7156603</v>
+        <v>7156504</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>undersidan av en granlåga med bla ullticka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128388375</v>
+        <v>128388765</v>
       </c>
       <c r="B4" t="n">
-        <v>91478</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774560</v>
+        <v>774246</v>
       </c>
       <c r="R4" t="n">
-        <v>7156580</v>
+        <v>7156504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128388385</v>
+        <v>128388540</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1006,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774561</v>
+        <v>774317</v>
       </c>
       <c r="R5" t="n">
-        <v>7156599</v>
+        <v>7156409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1076,17 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,46 +1105,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128388354</v>
+        <v>128388786</v>
       </c>
       <c r="B6" t="n">
-        <v>57827</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774556</v>
+        <v>774320</v>
       </c>
       <c r="R6" t="n">
-        <v>7156558</v>
+        <v>7156572</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1185,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,42 +1210,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128388540</v>
+        <v>128388375</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774317</v>
+        <v>774560</v>
       </c>
       <c r="R7" t="n">
-        <v>7156409</v>
+        <v>7156580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,17 +1290,13 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,6 +1312,540 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128388776</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>774320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7156572</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128388385</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>774561</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7156599</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128388428</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>774560</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7156603</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128388490</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>774374</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7156512</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128388354</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>774556</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7156558</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39114-2025 artfynd.xlsx
+++ b/artfynd/A 39114-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388575</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388786</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388375</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388765</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388776</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388385</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388428</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388490</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388540</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,8 +1901,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388354</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>